--- a/EinsatzPlanung/Assets/Excel/Themen.xlsx
+++ b/EinsatzPlanung/Assets/Excel/Themen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex\source\repos\EinsatzPlanung\EinsatzPlanung\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647005FB-7070-4D23-ACC2-D7A32E1D8FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E374E89-3494-4297-865E-46437C8C30BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{93971DC9-9131-4D11-831F-804A5976373C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{93971DC9-9131-4D11-831F-804A5976373C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Programmierung</t>
   </si>
   <si>
     <t>Netzwerke</t>
+  </si>
+  <si>
+    <t>Thema</t>
+  </si>
+  <si>
+    <t>Farbe</t>
+  </si>
+  <si>
+    <t>#ff00ff</t>
+  </si>
+  <si>
+    <t>#00ff00</t>
+  </si>
+  <si>
+    <t>Grundlagen</t>
+  </si>
+  <si>
+    <t>Projektmanagement</t>
+  </si>
+  <si>
+    <t>#ffff00</t>
+  </si>
+  <si>
+    <t>#0000ff</t>
+  </si>
+  <si>
+    <t>IT-Systeme</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>Dienste</t>
+  </si>
+  <si>
+    <t>Pruefungsvorbereitung</t>
+  </si>
+  <si>
+    <t>IT-Sicherheit</t>
+  </si>
+  <si>
+    <t>#5555ff</t>
+  </si>
+  <si>
+    <t>#ff5555</t>
+  </si>
+  <si>
+    <t>#ff55ff</t>
+  </si>
+  <si>
+    <t>#00ffff</t>
   </si>
 </sst>
 </file>
@@ -416,20 +467,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EA7A25F-1A13-43E6-8B5A-038B5C3A6F73}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
